--- a/data/trans_dic/P33B_R5-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R5-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,72</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,72</t>
+          <t>1,2; 6,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,17</t>
+          <t>1,15; 4,87</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,24</t>
+          <t>0,26; 2,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,33</t>
+          <t>1,72; 4,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,97</t>
+          <t>1,28; 3,38</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,72</t>
+          <t>2,27; 5,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,17</t>
+          <t>4,82; 8,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,23</t>
+          <t>3,9; 6,24</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,11</t>
+          <t>3,68; 7,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 12,23</t>
+          <t>8,0; 11,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,2</t>
+          <t>6,2; 8,88</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,76; 12,35</t>
+          <t>7,4; 11,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,83; 22,11</t>
+          <t>17,78; 22,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,83; 16,21</t>
+          <t>13,01; 16,51</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 15,06</t>
+          <t>9,55; 14,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,34; 19,96</t>
+          <t>16,61; 22,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,99; 16,4</t>
+          <t>14,07; 17,88</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,58; 22,86</t>
+          <t>15,79; 23,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,74; 30,68</t>
+          <t>25,05; 31,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,09; 26,96</t>
+          <t>22,12; 27,03</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,33</t>
+          <t>5,9; 7,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,54; 12,91</t>
+          <t>11,83; 13,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,83; 9,91</t>
+          <t>9,2; 10,42</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11133</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>18747</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 26864</t>
+          <t>0; 25337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3997; 24191</t>
+          <t>4363; 23922</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8385; 36900</t>
+          <t>8854; 37491</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>20821</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1080; 9499</t>
+          <t>1228; 13011</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6318; 22143</t>
+          <t>8607; 24655</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9868; 27787</t>
+          <t>12512; 33076</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33663</t>
+          <t>39615</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53992</t>
+          <t>61376</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11827; 30658</t>
+          <t>14067; 33450</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25189; 44322</t>
+          <t>29999; 50482</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41744; 67160</t>
+          <t>48535; 77611</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>34308</t>
+          <t>37266</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>68160</t>
+          <t>70716</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102468</t>
+          <t>107982</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14894; 54214</t>
+          <t>25768; 51012</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52711; 87146</t>
+          <t>58889; 85520</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60885; 131284</t>
+          <t>89071; 127646</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>54825</t>
+          <t>57581</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>106370</t>
+          <t>121041</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161196</t>
+          <t>178621</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43374; 69076</t>
+          <t>44959; 72841</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91810; 120634</t>
+          <t>108100; 137794</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>141777; 179078</t>
+          <t>158070; 200700</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>44329</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>77600</t>
+          <t>85460</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121929</t>
+          <t>134208</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>35200; 55451</t>
+          <t>38863; 59826</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32476; 121293</t>
+          <t>72832; 96900</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58434; 160068</t>
+          <t>118955; 151206</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>53893</t>
+          <t>59882</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>117743</t>
+          <t>130175</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>171636</t>
+          <t>190057</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44046; 64650</t>
+          <t>48986; 72501</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>105189; 130457</t>
+          <t>116232; 145085</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156382; 190901</t>
+          <t>171253; 209272</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>218916</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>427630</t>
+          <t>474236</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>646547</t>
+          <t>711812</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>168381; 253439</t>
+          <t>208439; 268293</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>348865; 472318</t>
+          <t>441591; 507802</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>557091; 705134</t>
+          <t>668340; 756581</t>
         </is>
       </c>
     </row>
